--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0108.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0108.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Nếu thấy tin này, hãy trả lời ta nhé.</t>
+          <t>Nếu thấy tin này, hãy trả lời tao nhé.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>...Giáo viên đang tìm ta. Ta phải lẻn ra ngoài một lát.</t>
+          <t>...Giáo viên đang tìm tao. Tao phải lẻn ra ngoài một lát.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
